--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:38</t>
+    <t xml:space="preserve">2026-09-09 22:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:24</t>
+    <t xml:space="preserve">2026-09-12 19:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_coquimbo.xlsx
@@ -42,30 +42,30 @@
     <t xml:space="preserve">Río Hurtado</t>
   </si>
   <si>
+    <t xml:space="preserve">Punitaqui</t>
+  </si>
+  <si>
     <t xml:space="preserve">Paihuano</t>
   </si>
   <si>
-    <t xml:space="preserve">Punitaqui</t>
+    <t xml:space="preserve">Combarbalá</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canela</t>
   </si>
   <si>
     <t xml:space="preserve">La Serena</t>
   </si>
   <si>
-    <t xml:space="preserve">Combarbalá</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canela</t>
-  </si>
-  <si>
     <t xml:space="preserve">Los Vilos</t>
   </si>
   <si>
+    <t xml:space="preserve">Andacollo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Vicuña</t>
   </si>
   <si>
-    <t xml:space="preserve">Andacollo</t>
-  </si>
-  <si>
     <t xml:space="preserve">Monte Patria</t>
   </si>
   <si>
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:41</t>
+    <t xml:space="preserve">2026-09-24 00:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -523,7 +523,7 @@
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>59.9</v>
+        <v>26.59</v>
       </c>
     </row>
     <row r="3">
@@ -540,7 +540,7 @@
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>46.27</v>
+        <v>20.27</v>
       </c>
     </row>
     <row r="4">
@@ -551,13 +551,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>4105</v>
+        <v>4304</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>42.35</v>
+        <v>19.63</v>
       </c>
     </row>
     <row r="5">
@@ -568,13 +568,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>4304</v>
+        <v>4105</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>41.58</v>
+        <v>18.77</v>
       </c>
     </row>
     <row r="6">
@@ -585,13 +585,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>4101</v>
+        <v>4302</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>36.79</v>
+        <v>18.74</v>
       </c>
     </row>
     <row r="7">
@@ -602,13 +602,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>4302</v>
+        <v>4202</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>36.16</v>
+        <v>18.03</v>
       </c>
     </row>
     <row r="8">
@@ -619,13 +619,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>4202</v>
+        <v>4101</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>35.44</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="9">
@@ -642,7 +642,7 @@
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>33.96</v>
+        <v>15.24</v>
       </c>
     </row>
     <row r="10">
@@ -650,16 +650,16 @@
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>4102</v>
+        <v>4103</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>32.09</v>
+        <v>14.77</v>
       </c>
     </row>
     <row r="11">
@@ -667,16 +667,16 @@
         <v>5</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>4106</v>
+        <v>4102</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>31.79</v>
+        <v>13.83</v>
       </c>
     </row>
     <row r="12">
@@ -687,13 +687,13 @@
         <v>15</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>4103</v>
+        <v>4106</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>30.36</v>
+        <v>13.29</v>
       </c>
     </row>
     <row r="13">
@@ -710,7 +710,7 @@
         <v>2023</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>26.83</v>
+        <v>11.58</v>
       </c>
     </row>
     <row r="14">
@@ -727,7 +727,7 @@
         <v>2023</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>23.58</v>
+        <v>10.06</v>
       </c>
     </row>
     <row r="15">
@@ -744,7 +744,7 @@
         <v>2023</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>20.91</v>
+        <v>9.42</v>
       </c>
     </row>
     <row r="16">
@@ -761,7 +761,7 @@
         <v>2023</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>20.83</v>
+        <v>9.19</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:18</t>
+    <t xml:space="preserve">2026-09-27 22:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:08</t>
+    <t xml:space="preserve">2026-09-29 11:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -523,7 +523,7 @@
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>26.59</v>
+        <v>265.94</v>
       </c>
     </row>
     <row r="3">
@@ -540,7 +540,7 @@
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>20.27</v>
+        <v>202.67</v>
       </c>
     </row>
     <row r="4">
@@ -557,7 +557,7 @@
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>19.63</v>
+        <v>196.27</v>
       </c>
     </row>
     <row r="5">
@@ -574,7 +574,7 @@
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>18.77</v>
+        <v>187.67</v>
       </c>
     </row>
     <row r="6">
@@ -591,7 +591,7 @@
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>18.74</v>
+        <v>187.35</v>
       </c>
     </row>
     <row r="7">
@@ -608,7 +608,7 @@
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>18.03</v>
+        <v>180.26</v>
       </c>
     </row>
     <row r="8">
@@ -625,7 +625,7 @@
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>16.2</v>
+        <v>161.96</v>
       </c>
     </row>
     <row r="9">
@@ -642,7 +642,7 @@
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>15.24</v>
+        <v>152.4</v>
       </c>
     </row>
     <row r="10">
@@ -659,7 +659,7 @@
         <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>14.77</v>
+        <v>147.75</v>
       </c>
     </row>
     <row r="11">
@@ -676,7 +676,7 @@
         <v>2023</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>13.83</v>
+        <v>138.3</v>
       </c>
     </row>
     <row r="12">
@@ -693,7 +693,7 @@
         <v>2023</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>13.29</v>
+        <v>132.92</v>
       </c>
     </row>
     <row r="13">
@@ -710,7 +710,7 @@
         <v>2023</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>11.58</v>
+        <v>115.77</v>
       </c>
     </row>
     <row r="14">
@@ -727,7 +727,7 @@
         <v>2023</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>10.06</v>
+        <v>100.62</v>
       </c>
     </row>
     <row r="15">
@@ -744,7 +744,7 @@
         <v>2023</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>9.42</v>
+        <v>94.24</v>
       </c>
     </row>
     <row r="16">
@@ -761,7 +761,7 @@
         <v>2023</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>9.19</v>
+        <v>91.89</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 11:02</t>
+    <t xml:space="preserve">2026-10-01 19:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:27</t>
+    <t xml:space="preserve">2026-10-02 13:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:06</t>
+    <t xml:space="preserve">2026-10-04 07:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 07:59</t>
+    <t xml:space="preserve">2026-10-05 07:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
